--- a/文档/城邦.xlsx
+++ b/文档/城邦.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Admin\Documents\GitHub\Sistine_civ6mod\文档\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D81C1DB-6990-4774-9584-63FE4FB3A406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -630,7 +624,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>🐎</t>
     </r>
@@ -643,13 +637,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>有学院的城市</t>
     </r>
     <r>
@@ -660,17 +647,17 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>农田+1食物，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+15%人口增长速度。</t>
+      <t>农田+1食物，+25%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>人口增长速度。</t>
     </r>
   </si>
   <si>
@@ -717,6 +704,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>通往外国的贸易路线</t>
     </r>
     <r>
@@ -817,6 +810,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>一条商路每长</t>
     </r>
     <r>
@@ -1226,8 +1226,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1249,34 +1255,351 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Emoji"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1284,13 +1607,255 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1300,180 +1865,111 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1484,7 +1980,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1512,40 +2008,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1795,14 +2405,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="24.375" customWidth="1"/>
     <col min="3" max="4" width="38.875" customWidth="1"/>
@@ -1811,7 +2421,7 @@
     <col min="8" max="8" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1834,983 +2444,983 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="27" spans="1:8">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="4" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
+    <row r="4" ht="27" spans="1:8">
+      <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="4" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="4" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="40.5" spans="1:8">
+      <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="4" t="s">
+      <c r="E6" s="3"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A7" s="4" t="s">
+    <row r="7" ht="27" spans="1:8">
+      <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="4" t="s">
+      <c r="E7" s="3"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="27" spans="1:8">
+      <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="4" t="s">
+      <c r="E8" s="3"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="4"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A10" s="4" t="s">
+    <row r="10" ht="27" spans="1:8">
+      <c r="A10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="4" t="s">
+      <c r="E10" s="3"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="3" t="s">
         <v>45</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:8">
+      <c r="A11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="4" t="s">
+      <c r="E11" s="3"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="27" spans="1:8">
+      <c r="A12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="4" t="s">
+      <c r="E12" s="3"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="3" t="s">
         <v>52</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A13" s="4" t="s">
+    <row r="13" ht="27" spans="1:8">
+      <c r="A13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="4" t="s">
+      <c r="E13" s="3"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A14" s="4" t="s">
+    <row r="14" ht="27" spans="1:8">
+      <c r="A14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="4" t="s">
+      <c r="E14" s="3"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:8">
+      <c r="A15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="4" t="s">
+      <c r="F15" s="5"/>
+      <c r="G15" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A16" s="4" t="s">
+    <row r="16" ht="27" spans="1:8">
+      <c r="A16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="4" t="s">
+      <c r="E16" s="3"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="3" t="s">
         <v>71</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="54" x14ac:dyDescent="0.15">
-      <c r="A17" s="4" t="s">
+    <row r="17" ht="54" spans="1:8">
+      <c r="A17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="4" t="s">
+      <c r="E17" s="3"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="3" t="s">
         <v>76</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A18" s="4" t="s">
+    <row r="18" ht="27" spans="1:8">
+      <c r="A18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="4" t="s">
+      <c r="E18" s="3"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="3" t="s">
         <v>81</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A19" s="4" t="s">
+    <row r="19" ht="27" spans="1:8">
+      <c r="A19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="4" t="s">
+      <c r="E19" s="3"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="3" t="s">
         <v>85</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A20" s="4" t="s">
+    <row r="20" ht="27" spans="1:8">
+      <c r="A20" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="4" t="s">
+      <c r="E20" s="3"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="3" t="s">
         <v>90</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A21" s="4" t="s">
+    <row r="21" ht="27" spans="1:8">
+      <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="4" t="s">
+      <c r="E21" s="3"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A22" s="4" t="s">
+    <row r="22" ht="27" spans="1:8">
+      <c r="A22" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="4" t="s">
+      <c r="E22" s="3"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="3" t="s">
         <v>96</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A23" s="4" t="s">
+    <row r="23" ht="27" spans="1:8">
+      <c r="A23" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="4" t="s">
+      <c r="E23" s="3"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="3" t="s">
         <v>100</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:8">
+      <c r="A24" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="4" t="s">
+      <c r="E24" s="3"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="3" t="s">
         <v>105</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A25" s="4" t="s">
+    <row r="25" ht="27" spans="1:8">
+      <c r="A25" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="4" t="s">
+      <c r="E25" s="3"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="3" t="s">
         <v>109</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A26" s="4" t="s">
+    <row r="26" ht="27" spans="1:8">
+      <c r="A26" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>113</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="4" t="s">
+      <c r="E26" s="3"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="3" t="s">
         <v>115</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A27" s="4" t="s">
+    <row r="27" ht="27" spans="1:8">
+      <c r="A27" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="4" t="s">
+      <c r="E27" s="3"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="3" t="s">
         <v>120</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:8">
+      <c r="A28" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="4" t="s">
+      <c r="E28" s="3"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="3" t="s">
         <v>124</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A29" s="4" t="s">
+    <row r="29" ht="27" spans="1:8">
+      <c r="A29" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="4" t="s">
+      <c r="F29" s="5"/>
+      <c r="G29" s="3" t="s">
         <v>129</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:8">
+      <c r="A30" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>132</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="4" t="s">
+      <c r="E30" s="3"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="3" t="s">
         <v>134</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A31" s="4" t="s">
+    <row r="31" ht="27" spans="1:8">
+      <c r="A31" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="4" t="s">
+      <c r="E31" s="3"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="3" t="s">
         <v>138</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:8">
+      <c r="A32" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="4" t="s">
+      <c r="E32" s="3"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="3" t="s">
         <v>142</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A33" s="4" t="s">
+    <row r="33" ht="27" spans="1:8">
+      <c r="A33" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="4" t="s">
+      <c r="E33" s="3"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="3" t="s">
         <v>147</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:8">
+      <c r="A34" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="4" t="s">
+      <c r="E34" s="3"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="3" t="s">
         <v>152</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:8">
+      <c r="A35" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="4" t="s">
+      <c r="E35" s="3"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="3" t="s">
         <v>156</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:8">
+      <c r="A36" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="4" t="s">
+      <c r="E36" s="3"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="3" t="s">
         <v>159</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A37" s="4" t="s">
+    <row r="37" ht="27" spans="1:8">
+      <c r="A37" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="4" t="s">
+      <c r="E37" s="3"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="3" t="s">
         <v>163</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A38" s="4" t="s">
+    <row r="38" ht="27" spans="1:8">
+      <c r="A38" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="4" t="s">
+      <c r="E38" s="3"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:8">
+      <c r="A39" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="4" t="s">
+      <c r="E39" s="3"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:8">
+      <c r="A40" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="4" t="s">
+      <c r="E40" s="3"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="3" t="s">
         <v>173</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A41" s="4" t="s">
+    <row r="41" ht="27" spans="1:8">
+      <c r="A41" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="4" t="s">
+      <c r="E41" s="3"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:8">
+      <c r="A42" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="4" t="s">
+      <c r="E42" s="3"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A43" s="4" t="s">
+    <row r="43" ht="27" spans="1:8">
+      <c r="A43" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="4" t="s">
+      <c r="E43" s="3"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="3" t="s">
         <v>186</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A44" s="4" t="s">
+    <row r="44" ht="27" spans="1:8">
+      <c r="A44" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="4" t="s">
+      <c r="E44" s="3"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A45" s="4" t="s">
+    <row r="45" spans="1:8">
+      <c r="A45" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="4" t="s">
+      <c r="E45" s="3"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A46" s="4" t="s">
+    <row r="46" spans="1:8">
+      <c r="A46" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="4" t="s">
+      <c r="E46" s="3"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A47" s="4" t="s">
+    <row r="47" ht="40.5" spans="1:8">
+      <c r="A47" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="4" t="s">
+      <c r="E47" s="3"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+    <row r="48" ht="27" spans="1:8">
       <c r="A48" s="1" t="s">
         <v>200</v>
       </c>
@@ -2820,7 +3430,7 @@
       <c r="C48" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E48" s="1"/>
@@ -2831,7 +3441,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+    <row r="49" ht="27" spans="1:8">
       <c r="A49" s="1" t="s">
         <v>203</v>
       </c>
@@ -2853,12 +3463,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E48">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H49" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <sortState ref="A2:E48">
     <sortCondition ref="B2:B48"/>
   </sortState>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>